--- a/Codes_2025/Trial 3/Trial3_ARIMAX_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_ARIMAX_Leaders_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,17 +609,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>21.01</v>
+        <v>37.81</v>
       </c>
       <c r="D6" t="n">
-        <v>22.46263821835457</v>
+        <v>37.78722367369897</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.452638218354569</v>
+        <v>0.02277632630102744</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>20.08</v>
+        <v>21.01</v>
       </c>
       <c r="D7" t="n">
-        <v>15.03220406324439</v>
+        <v>22.46263821835457</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -662,11 +662,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(2,1,0)</t>
+          <t>(2,1,1)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5.047795936755604</v>
+        <v>1.452638218354569</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -677,17 +677,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>9.359999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.621854949403332</v>
+        <v>15.03220406324439</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.2618549494033324</v>
+        <v>5.047795936755604</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>7.180000000000001</v>
+        <v>6.81</v>
       </c>
       <c r="D9" t="n">
-        <v>5.570951253236132</v>
+        <v>10.71819864477671</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.609048746763868</v>
+        <v>3.908198644776713</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>37.67999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>50.58855191775414</v>
+        <v>9.621854949403332</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>12.90855191775415</v>
+        <v>0.2618549494033324</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -779,17 +779,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.73</v>
+        <v>7.180000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1.904230677973479</v>
+        <v>5.570951253236132</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -798,11 +798,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(2,1,1)</t>
+          <t>(0,1,0)</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5.82576932202652</v>
+        <v>1.609048746763868</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>6.590000000000001</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>7.039289259277363</v>
+        <v>50.58855191775414</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -832,11 +832,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(2,1,1)</t>
+          <t>(2,1,0)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.4492892592773625</v>
+        <v>12.90855191775415</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -847,17 +847,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>10.19</v>
+        <v>7.73</v>
       </c>
       <c r="D13" t="n">
-        <v>8.547276150662915</v>
+        <v>1.904230677973479</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.642723849337083</v>
+        <v>5.82576932202652</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -881,32 +881,134 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24.26000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>37.37242473622501</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>(2,1,1)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>13.11242473622501</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7.039289259277363</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(2,1,1)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4492892592773625</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8.547276150662915</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(2,1,1)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1.642723849337083</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
         <v>37.58000000000002</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D17" t="n">
         <v>25.23204887958631</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>(2,1,0)</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="G17" t="n">
         <v>12.34795112041371</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Leaders</t>
         </is>
